--- a/Summary_Statistics.xlsx
+++ b/Summary_Statistics.xlsx
@@ -461,9 +461,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>GDP CAGR (%)</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Real GDP CAGR (%)</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -483,7 +483,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Median Household Income (RM)</t>
         </is>
@@ -505,7 +505,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Gini Coefficient</t>
         </is>
@@ -527,7 +527,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Absolute Poverty Rate (%)</t>
         </is>
@@ -549,9 +549,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Expenditure-to-Income Ratio</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Expenditure / Income Ratio</t>
         </is>
       </c>
       <c r="B6" t="n">
